--- a/Dataset_0/Ground Truth/Final_output_for_comparison.xlsx
+++ b/Dataset_0/Ground Truth/Final_output_for_comparison.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.4985333333333333</v>
+        <v>0.498533333333333</v>
       </c>
     </row>
     <row r="8">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.1311333333333333</v>
+        <v>0.131133333333333</v>
       </c>
     </row>
     <row r="9">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.1077783426537875</v>
+        <v>0.107778342653787</v>
       </c>
     </row>
     <row r="11">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.4016268429079817</v>
+        <v>0.401626842907982</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.3960345704117946</v>
+        <v>0.396034570411795</v>
       </c>
     </row>
     <row r="14">
@@ -504,6 +504,86 @@
       </c>
       <c r="B15">
         <v>0.0144617032672737</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fdr eQTM (no ref)</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.21259842519685</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3UTR</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5UTR</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>downstream</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>exon</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0.079</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>intergenic</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>intron</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.439</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>promoter</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.281</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_0/Ground Truth/Final_output_for_comparison.xlsx
+++ b/Dataset_0/Ground Truth/Final_output_for_comparison.xlsx
@@ -1,32 +1,100 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t xml:space="preserve">metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 genes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE_genes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CpG sites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CpG DM sites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct associations ratio (M2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both DE&amp;DM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dm_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recall eQTM (ref=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallout eQTM (ref&lt;0.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fdr eQTM (no ref)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3UTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5UTR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">downstream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intergenic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">promoter</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -52,17 +120,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -112,10 +176,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -141,15 +201,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -175,6 +232,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,243 +408,196 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>M2 genes</t>
-        </is>
-      </c>
-      <c r="B2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
         <v>5900</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DE_genes</t>
-        </is>
-      </c>
-      <c r="B3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
         <v>2942</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CpG sites</t>
-        </is>
-      </c>
-      <c r="B4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CpG DM sites</t>
-        </is>
-      </c>
-      <c r="B5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
         <v>7478</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Correct associations ratio (M2)</t>
-        </is>
-      </c>
-      <c r="B6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DM (any)</t>
-        </is>
-      </c>
-      <c r="B7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
         <v>0.498533333333333</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>both DE&amp;DM</t>
-        </is>
-      </c>
-      <c r="B8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
         <v>0.131133333333333</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>dm_only</t>
-        </is>
-      </c>
-      <c r="B9">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="n">
         <v>0.3674</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>q1</t>
-        </is>
-      </c>
-      <c r="B10">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="n">
         <v>0.107778342653787</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>q2</t>
-        </is>
-      </c>
-      <c r="B11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="n">
         <v>0.401626842907982</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>q3</t>
-        </is>
-      </c>
-      <c r="B12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="n">
         <v>0.0945602440264362</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>q4</t>
-        </is>
-      </c>
-      <c r="B13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="n">
         <v>0.396034570411795</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>recall eQTM (ref=1)</t>
-        </is>
-      </c>
-      <c r="B14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n">
         <v>0.97</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>fallout eQTM (ref&lt;0.05)</t>
-        </is>
-      </c>
-      <c r="B15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n">
         <v>0.0144617032672737</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>fdr eQTM (no ref)</t>
-        </is>
-      </c>
-      <c r="B16">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n">
         <v>0.21259842519685</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3UTR</t>
-        </is>
-      </c>
-      <c r="B17">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n">
         <v>0.016</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>5UTR</t>
-        </is>
-      </c>
-      <c r="B18">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n">
         <v>0.007</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>downstream</t>
-        </is>
-      </c>
-      <c r="B19">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n">
         <v>0.004</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>exon</t>
-        </is>
-      </c>
-      <c r="B20">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n">
         <v>0.079</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>intergenic</t>
-        </is>
-      </c>
-      <c r="B21">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n">
         <v>0.175</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>intron</t>
-        </is>
-      </c>
-      <c r="B22">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n">
         <v>0.439</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>promoter</t>
-        </is>
-      </c>
-      <c r="B23">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n">
         <v>0.281</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Dataset_0/Ground Truth/Final_output_for_comparison.xlsx
+++ b/Dataset_0/Ground Truth/Final_output_for_comparison.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">metric</t>
   </si>
@@ -63,6 +63,18 @@
   </si>
   <si>
     <t xml:space="preserve">fdr eQTM (no ref)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recall Delta (ref=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallout Delta (ref&lt;0.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fdr Delta (no ref)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overlap Delta∩eQTM (coord_key count)</t>
   </si>
   <si>
     <t xml:space="preserve">3UTR</t>
@@ -433,7 +445,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>2942</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +485,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.131133333333333</v>
+        <v>0.160933333333333</v>
       </c>
     </row>
     <row r="9">
@@ -481,7 +493,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3674</v>
+        <v>0.3376</v>
       </c>
     </row>
     <row r="10">
@@ -489,7 +501,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>0.107778342653787</v>
+        <v>0.0956917978458989</v>
       </c>
     </row>
     <row r="11">
@@ -497,7 +509,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>0.401626842907982</v>
+        <v>0.408864954432477</v>
       </c>
     </row>
     <row r="12">
@@ -505,7 +517,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0945602440264362</v>
+        <v>0.0990057995028998</v>
       </c>
     </row>
     <row r="13">
@@ -513,7 +525,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>0.396034570411795</v>
+        <v>0.396437448218724</v>
       </c>
     </row>
     <row r="14">
@@ -521,7 +533,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="15">
@@ -529,7 +541,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0144617032672737</v>
+        <v>0.0146931719965428</v>
       </c>
     </row>
     <row r="16">
@@ -537,7 +549,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="n">
-        <v>0.21259842519685</v>
+        <v>0.253731343283582</v>
       </c>
     </row>
     <row r="17">
@@ -545,7 +557,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="n">
-        <v>0.016</v>
+        <v>0.566666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -553,7 +565,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="n">
-        <v>0.007</v>
+        <v>0.00127442650807137</v>
       </c>
     </row>
     <row r="19">
@@ -561,7 +573,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="n">
-        <v>0.004</v>
+        <v>0.0476190476190476</v>
       </c>
     </row>
     <row r="20">
@@ -569,7 +581,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="n">
-        <v>0.079</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -577,7 +589,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="n">
-        <v>0.175</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="22">
@@ -585,7 +597,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="n">
-        <v>0.439</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="23">
@@ -593,6 +605,38 @@
         <v>23</v>
       </c>
       <c r="B23" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.079</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.439</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="n">
         <v>0.281</v>
       </c>
     </row>
